--- a/rcads/data/xls/04_EntityGroups.xlsx
+++ b/rcads/data/xls/04_EntityGroups.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="_04_EntityGroups"/>
   </sheets>
   <definedNames>
-    <definedName name="_04_EntityGroups">'_04_EntityGroups'!$A$1:$B$161</definedName>
+    <definedName name="_04_EntityGroups">'_04_EntityGroups'!$A$1:$B$179</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -343,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B161"/>
+  <dimension ref="A1:B179"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -1958,6 +1958,186 @@
         </is>
       </c>
     </row>
+    <row outlineLevel="0" r="162">
+      <c r="A162" s="0">
+        <v>166</v>
+      </c>
+      <c r="B162" s="0" t="inlineStr">
+        <is>
+          <t>RCADS-25-Y-IT</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="163">
+      <c r="A163" s="0">
+        <v>167</v>
+      </c>
+      <c r="B163" s="0" t="inlineStr">
+        <is>
+          <t>[2] RCADS-47-Y-IT, RCADS-25-Y-EN</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="164">
+      <c r="A164" s="0">
+        <v>168</v>
+      </c>
+      <c r="B164" s="0" t="inlineStr">
+        <is>
+          <t>RCADS-25-CG-IT</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="165">
+      <c r="A165" s="0">
+        <v>169</v>
+      </c>
+      <c r="B165" s="0" t="inlineStr">
+        <is>
+          <t>[2] RCADS-47-CG-IT, RCADS-25-CG-EN</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="166">
+      <c r="A166" s="0">
+        <v>170</v>
+      </c>
+      <c r="B166" s="0" t="inlineStr">
+        <is>
+          <t>RCADS-47-Y-MR</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="167">
+      <c r="A167" s="0">
+        <v>171</v>
+      </c>
+      <c r="B167" s="0" t="inlineStr">
+        <is>
+          <t>RCADS-47-CG-MR</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="168">
+      <c r="A168" s="0">
+        <v>172</v>
+      </c>
+      <c r="B168" s="0" t="inlineStr">
+        <is>
+          <t>RCADS-47-Y-ZU</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="169">
+      <c r="A169" s="0">
+        <v>173</v>
+      </c>
+      <c r="B169" s="0" t="inlineStr">
+        <is>
+          <t>RCADS-47-CG-ZU</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="170">
+      <c r="A170" s="0">
+        <v>174</v>
+      </c>
+      <c r="B170" s="0" t="inlineStr">
+        <is>
+          <t>RCADS-47-Y-VI</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="171">
+      <c r="A171" s="0">
+        <v>175</v>
+      </c>
+      <c r="B171" s="0" t="inlineStr">
+        <is>
+          <t>RCADS-47-CG-VI</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="172">
+      <c r="A172" s="0">
+        <v>176</v>
+      </c>
+      <c r="B172" s="0" t="inlineStr">
+        <is>
+          <t>RCADS-25-Y-ZU</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="173">
+      <c r="A173" s="0">
+        <v>177</v>
+      </c>
+      <c r="B173" s="0" t="inlineStr">
+        <is>
+          <t>RCADS-25-CG-ZU</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="174">
+      <c r="A174" s="0">
+        <v>178</v>
+      </c>
+      <c r="B174" s="0" t="inlineStr">
+        <is>
+          <t>[2] RCADS-47-Y-ZU, RCADS-25-Y-EN</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="175">
+      <c r="A175" s="0">
+        <v>179</v>
+      </c>
+      <c r="B175" s="0" t="inlineStr">
+        <is>
+          <t>[2] RCADS-47-CG-ZU, RCADS-25-CG-EN</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="176">
+      <c r="A176" s="0">
+        <v>180</v>
+      </c>
+      <c r="B176" s="0" t="inlineStr">
+        <is>
+          <t>RCADS-25-Y-MR</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="177">
+      <c r="A177" s="0">
+        <v>181</v>
+      </c>
+      <c r="B177" s="0" t="inlineStr">
+        <is>
+          <t>RCADS-25-CG-MR</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="178">
+      <c r="A178" s="0">
+        <v>182</v>
+      </c>
+      <c r="B178" s="0" t="inlineStr">
+        <is>
+          <t>[2] RCADS-47-Y-MR, RCADS-25-Y-EN</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="179">
+      <c r="A179" s="0">
+        <v>183</v>
+      </c>
+      <c r="B179" s="0" t="inlineStr">
+        <is>
+          <t>[2] RCADS-47-CG-MR, RCADS-25-CG-EN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
